--- a/data/raw/김포 25년/항공통계상세조회(노선) (6).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (6).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10484</t>
-  </si>
-  <si>
-    <t>1870648</t>
-  </si>
-  <si>
-    <t>15151</t>
+    <t>5246</t>
+  </si>
+  <si>
+    <t>937375</t>
+  </si>
+  <si>
+    <t>7843</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,169 +53,172 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>76168</t>
-  </si>
-  <si>
-    <t>883</t>
+    <t>210</t>
+  </si>
+  <si>
+    <t>37238</t>
+  </si>
+  <si>
+    <t>454</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>6431</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>619</t>
+  </si>
+  <si>
+    <t>91471</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>4693</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>4844</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>80013</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>13026</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>6634</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>9952</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>9102</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>10487</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3370</t>
+  </si>
+  <si>
+    <t>627700</t>
+  </si>
+  <si>
+    <t>4096</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>5836</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>1658</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>120</t>
   </si>
   <si>
-    <t>13256</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1233</t>
-  </si>
-  <si>
-    <t>182376</t>
-  </si>
-  <si>
-    <t>715</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>9552</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>9747</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>720</t>
-  </si>
-  <si>
-    <t>159300</t>
-  </si>
-  <si>
-    <t>2870</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>25713</t>
-  </si>
-  <si>
-    <t>294</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>13496</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20002</t>
-  </si>
-  <si>
-    <t>242</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>171</t>
-  </si>
-  <si>
-    <t>18908</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>21549</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6735</t>
-  </si>
-  <si>
-    <t>1249185</t>
-  </si>
-  <si>
-    <t>8571</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>11804</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>3337</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>56255</t>
-  </si>
-  <si>
-    <t>1031</t>
+    <t>28290</t>
+  </si>
+  <si>
+    <t>339</t>
   </si>
 </sst>
 </file>
@@ -506,7 +509,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -517,16 +520,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="0">
         <v>36</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -537,16 +540,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -557,16 +560,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -577,16 +580,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -597,16 +600,16 @@
         <v>11</v>
       </c>
       <c r="C17" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
